--- a/data/trans_orig/CAGE_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2007</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3887</t>
+          <t>4023</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10563</t>
+          <t>11928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5860</t>
+          <t>5568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20845</t>
+          <t>21599</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1015528</t>
+          <t>1014983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1027836</t>
+          <t>1027700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1304550</t>
+          <t>1303185</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2325990</t>
+          <t>2325236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2340975</t>
+          <t>2341267</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,76%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8086</t>
+          <t>7266</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23535</t>
+          <t>22502</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>1014</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10518</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10657</t>
+          <t>10948</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27764</t>
+          <t>27987</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1669878</t>
+          <t>1670911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1685327</t>
+          <t>1686147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1577155</t>
+          <t>1577370</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1586505</t>
+          <t>1586659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,93%</t>
+          <t>99,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3253322</t>
+          <t>3253099</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3270429</t>
+          <t>3270138</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,67%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>850</t>
+          <t>848</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9753</t>
+          <t>9628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>7185</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12498</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541655</t>
+          <t>541780</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550558</t>
+          <t>550560</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>468645</t>
+          <t>469227</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015322</t>
+          <t>1015008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1025827</t>
+          <t>1025937</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17045</t>
+          <t>17014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38902</t>
+          <t>38046</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>4326</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17659</t>
+          <t>18367</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,47 +1812,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>24204</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>47707</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>24809</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>48344</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3237641</t>
+          <t>3238497</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3259498</t>
+          <t>3259529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3361538</t>
+          <t>3360830</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3375477</t>
+          <t>3374871</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,47 +1925,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>99,46%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,87%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6608034</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6631537</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,89%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6607397</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6630932</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2012</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30709</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2059</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9770</t>
+          <t>10070</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>29808</t>
+          <t>30480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>943934</t>
+          <t>944069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>964607</t>
+          <t>964758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1335738</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1337797</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2282632</t>
+          <t>2281960</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2302670</t>
+          <t>2302370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>31012</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56559</t>
+          <t>56382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>1998</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35262</t>
+          <t>34463</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61678</t>
+          <t>61318</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,65%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1907398</t>
+          <t>1907575</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1932945</t>
+          <t>1933209</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1746161</t>
+          <t>1745485</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1755796</t>
+          <t>1755805</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3660082</t>
+          <t>3660442</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3686498</t>
+          <t>3687297</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1710</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15621</t>
+          <t>14465</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1985</t>
+          <t>1699</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19383</t>
+          <t>15702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>465560</t>
+          <t>466716</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>479471</t>
+          <t>480038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,76%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>456499</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>458631</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>920430</t>
+          <t>924111</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937828</t>
+          <t>938114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,79%</t>
+          <t>99,82%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50690</t>
+          <t>50228</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86263</t>
+          <t>84968</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11312</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>54981</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>90328</t>
+          <t>89996</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3333519</t>
+          <t>3334814</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369092</t>
+          <t>3369554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3542246</t>
+          <t>3542918</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3552239</t>
+          <t>3552237</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,66%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6883684</t>
+          <t>6884016</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6918703</t>
+          <t>6919031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2016</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9289</t>
+          <t>9847</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27119</t>
+          <t>27525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7244</t>
+          <t>5779</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10086</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>28779</t>
+          <t>30224</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>727228</t>
+          <t>726822</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>745058</t>
+          <t>744500</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>987416</t>
+          <t>988881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1720228</t>
+          <t>1718783</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1738921</t>
+          <t>1738623</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19192</t>
+          <t>19147</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>41441</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4386</t>
+          <t>4338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>16707</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4337,7 +4337,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27066</t>
+          <t>25506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52542</t>
+          <t>49955</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,23%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2034488</t>
+          <t>2034944</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2057193</t>
+          <t>2057238</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1971593</t>
+          <t>1970883</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1983914</t>
+          <t>1983962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,7 +4445,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4012143</t>
+          <t>4014730</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4037619</t>
+          <t>4039179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>957</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14288</t>
+          <t>12589</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14658</t>
+          <t>14518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4807</t>
+          <t>4947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20693</t>
+          <t>20051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>532598</t>
+          <t>534297</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545927</t>
+          <t>545929</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534482</t>
+          <t>534622</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>546347</t>
+          <t>546344</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075334</t>
+          <t>1075976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091220</t>
+          <t>1091080</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35584</t>
+          <t>37090</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65569</t>
+          <t>65170</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9651</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26771</t>
+          <t>27603</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5023,7 +5023,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49924</t>
+          <t>50793</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85389</t>
+          <t>84445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,22%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3312049</t>
+          <t>3312448</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3342034</t>
+          <t>3340528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3505329</t>
+          <t>3504497</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3522449</t>
+          <t>3522732</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6824329</t>
+          <t>6825273</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6859794</t>
+          <t>6858925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con consumo de riesgo, consumo perudicial o dependencia al alcohol (CAGE) en 2023</t>
+          <t>Población con consumo de riesgo, consumo perjudicial o dependencia al alcohol (CAGE) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8136</t>
+          <t>8405</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>24239</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5582,7 +5582,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9395</t>
+          <t>9367</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>25937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219056</t>
+          <t>219017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>235120</t>
+          <t>234851</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64727</t>
+          <t>64398</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -5705,7 +5705,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>285176</t>
+          <t>284652</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301194</t>
+          <t>301222</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,82%</t>
+          <t>91,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6715</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21445</t>
+          <t>21216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2461</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>19195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12752</t>
+          <t>12214</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34262</t>
+          <t>33351</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959630</t>
+          <t>959859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>974360</t>
+          <t>974342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>685240</t>
+          <t>685141</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>701875</t>
+          <t>701346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1651148</t>
+          <t>1652059</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1672658</t>
+          <t>1673196</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4427</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16088</t>
+          <t>15656</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7299</t>
+          <t>7348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18837</t>
+          <t>19326</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>326852</t>
+          <t>327284</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338482</t>
+          <t>338513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233887</t>
+          <t>233838</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239962</t>
+          <t>239914</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>565289</t>
+          <t>564800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>577482</t>
+          <t>577438</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25553</t>
+          <t>25651</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50066</t>
+          <t>50099</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6134</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23820</t>
+          <t>22873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>32572</t>
+          <t>32691</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63738</t>
+          <t>63974</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1517204</t>
+          <t>1517171</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1541717</t>
+          <t>1541619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>989035</t>
+          <t>989982</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1006721</t>
+          <t>1007144</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2516387</t>
+          <t>2516151</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2547553</t>
+          <t>2547434</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CAGE_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/CAGE_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>17246</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>10790</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21599</t>
+          <t>21138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1014983</t>
+          <t>1014477</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1027700</t>
+          <t>1027767</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1303185</t>
+          <t>1304323</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2325236</t>
+          <t>2325697</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2341267</t>
+          <t>2340813</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7266</t>
+          <t>7661</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22502</t>
+          <t>23016</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10126</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10915</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>27987</t>
+          <t>27289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1670911</t>
+          <t>1670397</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1686147</t>
+          <t>1685752</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1577370</t>
+          <t>1577547</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1586659</t>
+          <t>1586504</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,94%</t>
+          <t>99,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3253099</t>
+          <t>3253797</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3270138</t>
+          <t>3270171</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>847</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9628</t>
+          <t>9325</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7185</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1880</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>13172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>541780</t>
+          <t>542083</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>550560</t>
+          <t>550561</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>469227</t>
+          <t>470196</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1015008</t>
+          <t>1014648</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1025937</t>
+          <t>1025940</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17014</t>
+          <t>16852</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38046</t>
+          <t>37973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,82 +1777,82 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>9289</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4632</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18511</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>34927</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>24974</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>48973</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9289</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>18367</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>34927</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>24204</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>47707</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3238497</t>
+          <t>3238570</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3259529</t>
+          <t>3259691</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1895,77 +1895,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>99,49%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3289</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>3369908</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3360686</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3374565</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,73%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>99,86%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6620814</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6606768</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6630767</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>99,48%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>3289</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3369908</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3360830</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3374871</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,73%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,87%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6478</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6620814</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6608034</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6631537</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>99,48%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9885</t>
+          <t>10489</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>32276</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10070</t>
+          <t>10137</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>30480</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>944069</t>
+          <t>942367</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>964758</t>
+          <t>964154</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2281960</t>
+          <t>2281903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2302370</t>
+          <t>2302303</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30748</t>
+          <t>29936</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56382</t>
+          <t>55764</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1998</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12318</t>
+          <t>11245</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34463</t>
+          <t>35916</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>61318</t>
+          <t>62289</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1907575</t>
+          <t>1908193</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1933209</t>
+          <t>1934021</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1745485</t>
+          <t>1746558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1755805</t>
+          <t>1755802</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,7 +2842,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3660442</t>
+          <t>3659471</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3687297</t>
+          <t>3685844</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1143</t>
+          <t>1715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14465</t>
+          <t>16235</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1699</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15702</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>466716</t>
+          <t>464946</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480038</t>
+          <t>479466</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>924111</t>
+          <t>923940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>938114</t>
+          <t>938091</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50228</t>
+          <t>50485</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84968</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1993</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>11416</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>54981</t>
+          <t>54042</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>89996</t>
+          <t>89752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3334814</t>
+          <t>3335295</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3369554</t>
+          <t>3369297</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3542918</t>
+          <t>3542814</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3552237</t>
+          <t>3552229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6884016</t>
+          <t>6884260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6919031</t>
+          <t>6919970</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,23%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27525</t>
+          <t>26412</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5779</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3994,42 +3994,42 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>17512</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>10156</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>28166</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,0%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>17512</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>10384</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>30224</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>726822</t>
+          <t>727935</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>744500</t>
+          <t>745729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>988881</t>
+          <t>987521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4102,47 +4102,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>99,28%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1638</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1731495</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1720841</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>1738851</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>99,0%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>99,42%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1638</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1731495</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>1718783</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>1738623</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>99,41%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>19115</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41441</t>
+          <t>41179</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4338</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>18574</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>27436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>49955</t>
+          <t>50216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2034944</t>
+          <t>2035206</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2057238</t>
+          <t>2057270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1970883</t>
+          <t>1969726</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1983962</t>
+          <t>1983427</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4014730</t>
+          <t>4014469</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4039179</t>
+          <t>4037249</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,33%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12589</t>
+          <t>14350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2807</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4947</t>
+          <t>4883</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20051</t>
+          <t>20312</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534297</t>
+          <t>532536</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545929</t>
+          <t>545915</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>534622</t>
+          <t>534066</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>546344</t>
+          <t>546333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1075976</t>
+          <t>1075715</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1091080</t>
+          <t>1091144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,7 +4823,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>37090</t>
+          <t>35015</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65170</t>
+          <t>63766</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>10455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27603</t>
+          <t>28255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50793</t>
+          <t>50988</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84445</t>
+          <t>83179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3312448</t>
+          <t>3313852</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3340528</t>
+          <t>3342603</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3504497</t>
+          <t>3503845</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3522732</t>
+          <t>3521645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6825273</t>
+          <t>6826539</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6858925</t>
+          <t>6858730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>14965</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24239</t>
+          <t>24102</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,7 +5572,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>854</t>
+          <t>888</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -5582,12 +5582,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2935</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>15206</t>
+          <t>15853</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>9420</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25937</t>
+          <t>24956</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>7,5%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>228904</t>
+          <t>242762</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>219017</t>
+          <t>233625</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>234851</t>
+          <t>248592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,27 +5685,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66479</t>
+          <t>74045</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64398</t>
+          <t>71854</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>295383</t>
+          <t>316808</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>284652</t>
+          <t>307705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301222</t>
+          <t>323241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,17%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>243256</t>
+          <t>257727</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67333</t>
+          <t>74933</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>310589</t>
+          <t>332661</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>12572</t>
+          <t>15286</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6733</t>
+          <t>8350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21216</t>
+          <t>27202</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9194</t>
+          <t>11580</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2990</t>
+          <t>5362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19195</t>
+          <t>22151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21766</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>17197</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>33351</t>
+          <t>40064</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>968503</t>
+          <t>1025361</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>959859</t>
+          <t>1013445</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>974342</t>
+          <t>1032297</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>695142</t>
+          <t>542291</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>685141</t>
+          <t>531720</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>701346</t>
+          <t>548509</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1663644</t>
+          <t>1567652</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1652059</t>
+          <t>1554454</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1673196</t>
+          <t>1577321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>981075</t>
+          <t>1040647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>704336</t>
+          <t>553871</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1685410</t>
+          <t>1594518</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>8382</t>
+          <t>10960</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4427</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15656</t>
+          <t>18197</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3311</t>
+          <t>4179</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7348</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6688</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19326</t>
+          <t>23419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>334558</t>
+          <t>355736</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>327284</t>
+          <t>348499</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>338513</t>
+          <t>360605</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>237875</t>
+          <t>260690</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233838</t>
+          <t>256201</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239914</t>
+          <t>263400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>572433</t>
+          <t>616426</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>564800</t>
+          <t>608145</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>577438</t>
+          <t>622362</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,54%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>342940</t>
+          <t>366696</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>241186</t>
+          <t>264869</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>631564</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35306</t>
+          <t>41211</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25651</t>
+          <t>29559</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50099</t>
+          <t>55076</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,67 +6601,67 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5711</t>
+          <t>9748</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>22873</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
+          <t>3,17%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>57858</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>43483</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>75582</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>2,26%</t>
         </is>
       </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>48664</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>32691</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>63974</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,95%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1531964</t>
+          <t>1623858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1517171</t>
+          <t>1609993</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1541619</t>
+          <t>1635510</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,67 +6714,67 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>999496</t>
+          <t>877027</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>989982</t>
+          <t>865385</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1007144</t>
+          <t>883926</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>96,83%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>98,91%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2500885</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2483161</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>2515260</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>97,74%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,44%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2700</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>2531461</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>2516151</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2547434</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,11%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1567270</t>
+          <t>1665069</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1012855</t>
+          <t>893674</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2580125</t>
+          <t>2558743</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
